--- a/files/22-222-228-idaho-ave.xlsx
+++ b/files/22-222-228-idaho-ave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iniculete\LAAA-Deploys\onmarket\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2636B56D-F01C-48C6-9F1C-F84BD2926B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6A8DA51-18C4-4ECD-9EE0-3E3CFBDC10A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{54DF3590-E6B8-41DF-8528-EA26CCF9784C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D5539255-B69F-4543-B41B-0450F8F154A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="142">
   <si>
     <t>LAAA UNDERWRITING BENCHMARKS (edit here; every deal tab reads these)</t>
   </si>
@@ -192,10 +192,10 @@
     <t>LoopNet listing</t>
   </si>
   <si>
-    <t>Data pulled 9/17/2026 from LoopNet public listing</t>
-  </si>
-  <si>
-    <t>NOTE: Two parcels 222 &amp; 228 Idaho</t>
+    <t>Data pulled 9/17/2026 from LoopNet public listing + rent roll and expenses read from the listing broker's OM (Lee &amp; Associates, Berzack, rent roll 9/1/2026)</t>
+  </si>
+  <si>
+    <t>NOTE: Two parcels 222 &amp; 228 Idaho | OM: Unit-by-unit rents sum to exactly $50,436/mo; OM annual $605,232 = 12 x $50,436 (matches).; Unit 228-3 (1+1) is VACANT; its $2,800 is the OM's asking rent, included in current GSR per OM.; Three units are owner occupied and 'can be delivered vacant' (228-1 $2,750, 228-6 $3,595, 228-10 $2,800); the O | OM: Unit-by-unit rents sum to exactly $50,436/mo; OM annual $605,232 = 12 x $50,436 (matches).; Unit 228-3 (1+1) is VACANT; its $2,800 is the OM's asking rent, included in current GSR per OM.; Three units are owner occupied and 'can be delivered vacant' (228-1 $2,750, 228-6 $3,595, 228-10 $2,800); the O</t>
   </si>
   <si>
     <t>PROPERTY</t>
@@ -297,13 +297,16 @@
     <t>Rent source</t>
   </si>
   <si>
-    <t>Allocated from published GRM (price / GRM) using LAAA bed weights</t>
-  </si>
-  <si>
-    <t>1 Bd / 1 Ba</t>
-  </si>
-  <si>
-    <t>2 Bd / 2 Ba</t>
+    <t>Studio / 1 Ba  [OM market/asking rent 2395; OM avg shown 2,298]</t>
+  </si>
+  <si>
+    <t>OM rent roll, current in-place rents (OM rent roll 9/1/2026)</t>
+  </si>
+  <si>
+    <t>1 Bd / 1 Ba  [OM market/asking rent 2775; OM avg shown 2,465; includes vac]</t>
+  </si>
+  <si>
+    <t>2 Bd / 2 Ba  [OM market/asking rent 3595; OM avg shown 3,204; 228-6 owner-]</t>
   </si>
   <si>
     <t>Total / weighted avg</t>
@@ -324,7 +327,7 @@
     <t>Scheduled gross rent</t>
   </si>
   <si>
-    <t>OM column: price / published GRM</t>
+    <t>OM column: OM stated current scheduled rent (OM rent roll 9/1/2026); LAAA column: OM rent roll by unit type</t>
   </si>
   <si>
     <t>Other income (laundry, parking, RUBS)</t>
@@ -336,7 +339,7 @@
     <t>Vacancy &amp; credit loss</t>
   </si>
   <si>
-    <t>OM 3.0% (OM figure if extracted, else 3% assumed); LAAA per Assumptions</t>
+    <t>OM 3.0%; LAAA per Assumptions</t>
   </si>
   <si>
     <t>Effective gross income</t>
@@ -381,7 +384,7 @@
     <t>Utilities (water/sewer/trash/common electric &amp; gas)</t>
   </si>
   <si>
-    <t>per unit, by city</t>
+    <t>per unit, by city; OM utilities + water/sewer + gas/electric + trash combined</t>
   </si>
   <si>
     <t>Contract services (landscape, pest, cleaning)</t>
@@ -390,10 +393,10 @@
     <t>per unit</t>
   </si>
   <si>
-    <t>Admin / legal / licenses / rent registration</t>
-  </si>
-  <si>
-    <t>per unit; OM "other" items land here</t>
+    <t>Admin / legal / licenses / rent registration / other OM items</t>
+  </si>
+  <si>
+    <t>OM other items: On-Site Management 14,400; S.M. Unit Registration 4,800; Miscellaneous ($100/unit) 2,000</t>
   </si>
   <si>
     <t>Replacement reserves</t>
@@ -402,7 +405,7 @@
     <t>Total operating expenses</t>
   </si>
   <si>
-    <t>OM line items not published. OM total IMPLIED = OM EGI - (price x published cap)</t>
+    <t>OM line items from OM (OM rent roll 9/1/2026); basis: OM 'Estimated Annual Expenses' (broker estimates, same $217,743 applied to both Current and Market columns). Taxes est. 1.25% of price; R&amp;M $2/SF on 15,640 SF; off-site management 4% of GOI ($631,632); utilities is a single combined line. Vacancy reserve 3% of GOI ($18,949) is shown as a deduction to EGI, not an expense line. Line items sum to $217,743 exactly.; OM total 217,743</t>
   </si>
   <si>
     <t>Expenses per unit</t>
@@ -418,6 +421,9 @@
   </si>
   <si>
     <t>Net operating income</t>
+  </si>
+  <si>
+    <t>OM states NOI 394,940 / cap 5.07</t>
   </si>
   <si>
     <t>Cap rate on asking price</t>
@@ -466,12 +472,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="\$#,##0;\(\$#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0;\(&quot;$&quot;#,##0\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -519,6 +526,7 @@
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -527,8 +535,21 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -556,7 +577,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF9E5"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -592,7 +614,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -616,12 +638,15 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -654,7 +679,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2D1140C-47B4-4954-A10C-8EE31885DD8B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{795909FD-955F-408B-9F94-8CAF09766150}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -965,7 +990,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC59745E-33FF-4EBE-B341-94AC2E850E43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4917C3AA-E721-4D18-85F3-44C369FA02A9}">
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1334,7 +1359,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE1A206-F165-40CA-8088-23ECE69471F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7B119C1-5B8F-45E6-94E8-9F3DDDCBF039}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1559,94 +1584,94 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="B30" s="15">
         <v>2</v>
       </c>
       <c r="C30" s="21">
-        <v>1833</v>
-      </c>
-      <c r="D30" s="8">
+        <v>2298</v>
+      </c>
+      <c r="D30" s="22">
         <f>B30*C30</f>
-        <v>3666</v>
-      </c>
-      <c r="E30" s="8">
+        <v>4596</v>
+      </c>
+      <c r="E30" s="22">
         <f>D30*12</f>
-        <v>43992</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>85</v>
+        <v>55152</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B31" s="15">
         <v>16</v>
       </c>
       <c r="C31" s="21">
-        <v>2619</v>
-      </c>
-      <c r="D31" s="8">
+        <v>2465</v>
+      </c>
+      <c r="D31" s="22">
         <f>B31*C31</f>
-        <v>41904</v>
-      </c>
-      <c r="E31" s="8">
+        <v>39440</v>
+      </c>
+      <c r="E31" s="22">
         <f>D31*12</f>
-        <v>502848</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>85</v>
+        <v>473280</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B32" s="15">
         <v>2</v>
       </c>
       <c r="C32" s="21">
-        <v>3536</v>
-      </c>
-      <c r="D32" s="8">
+        <v>3204</v>
+      </c>
+      <c r="D32" s="22">
         <f>B32*C32</f>
-        <v>7072</v>
-      </c>
-      <c r="E32" s="8">
+        <v>6408</v>
+      </c>
+      <c r="E32" s="22">
         <f>D32*12</f>
-        <v>84864</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>85</v>
+        <v>76896</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="B33" s="23">
+      <c r="A33" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" s="25">
         <f>SUM(B30:B32)</f>
         <v>20</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="26">
         <f>IFERROR(D33/B33,"")</f>
-        <v>2632.1</v>
-      </c>
-      <c r="D33" s="24">
+        <v>2522.1999999999998</v>
+      </c>
+      <c r="D33" s="26">
         <f>SUM(D30:D32)</f>
-        <v>52642</v>
-      </c>
-      <c r="E33" s="24">
+        <v>50444</v>
+      </c>
+      <c r="E33" s="26">
         <f>SUM(E30:E32)</f>
-        <v>631704</v>
+        <v>605328</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
@@ -1655,90 +1680,90 @@
       <c r="F35" s="14"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="25"/>
-      <c r="B36" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="25" t="s">
+      <c r="A36" s="27"/>
+      <c r="B36" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25" t="s">
+      <c r="C36" s="27" t="s">
         <v>92</v>
+      </c>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>93</v>
-      </c>
-      <c r="B37" s="8">
-        <v>631685.57536466781</v>
+        <v>94</v>
+      </c>
+      <c r="B37" s="22">
+        <v>605232</v>
       </c>
       <c r="C37" s="8">
         <f>E33</f>
-        <v>631704</v>
+        <v>605328</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B38" s="8">
-        <v>0</v>
+        <v>26400</v>
       </c>
       <c r="C38" s="4">
-        <v>0</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="22" t="s">
-        <v>96</v>
+      <c r="A39" s="24" t="s">
+        <v>97</v>
       </c>
       <c r="B39" s="8">
         <f>B37+B38</f>
-        <v>631685.57536466781</v>
+        <v>631632</v>
       </c>
       <c r="C39" s="8">
         <f>C37+C38</f>
-        <v>631704</v>
+        <v>631728</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B40" s="8">
         <f>-B37*0.03</f>
-        <v>-18950.567260940032</v>
+        <v>-18156.96</v>
       </c>
       <c r="C40" s="8">
         <f>-C37*Assumptions!$B$3</f>
-        <v>-18951.12</v>
+        <v>-18159.84</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="B41" s="24">
+      <c r="A41" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="26">
         <f>B39+B40</f>
-        <v>612735.00810372783</v>
-      </c>
-      <c r="C41" s="24">
+        <v>613475.04</v>
+      </c>
+      <c r="C41" s="26">
         <f>C39+C40</f>
-        <v>612752.88</v>
+        <v>613568.16</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
@@ -1747,182 +1772,196 @@
       <c r="F43" s="14"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="B44" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" s="25" t="s">
+      <c r="A44" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="D44" s="25" t="s">
+      <c r="B44" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="E44" s="25" t="s">
+      <c r="C44" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="F44" s="25" t="s">
+      <c r="D44" s="27" t="s">
         <v>92</v>
+      </c>
+      <c r="E44" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="F44" s="27" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>104</v>
-      </c>
-      <c r="B45" s="8"/>
+        <v>105</v>
+      </c>
+      <c r="B45" s="22">
+        <v>97438</v>
+      </c>
       <c r="C45" s="8">
         <f>B22*Assumptions!$B$16</f>
         <v>89642.5</v>
       </c>
-      <c r="D45" s="26">
+      <c r="D45" s="28">
         <f>C45</f>
         <v>89642.5</v>
       </c>
-      <c r="E45" s="8" t="str">
+      <c r="E45" s="8">
         <f t="shared" ref="E45:E53" si="0">IF(ISNUMBER(B45),D45-B45,"")</f>
-        <v/>
+        <v>-7795.5</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>106</v>
-      </c>
-      <c r="B46" s="8"/>
+        <v>107</v>
+      </c>
+      <c r="B46" s="22">
+        <v>18498</v>
+      </c>
       <c r="C46" s="8">
         <f>B7*Assumptions!$B$5+B8*Assumptions!$B$6</f>
         <v>19006</v>
       </c>
-      <c r="D46" s="26">
+      <c r="D46" s="28">
         <f t="shared" ref="D46:D52" si="1">IF(ISNUMBER(B46),MAX(B46,C46),C46)</f>
         <v>19006</v>
       </c>
-      <c r="E46" s="8" t="str">
+      <c r="E46" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>508</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>108</v>
-      </c>
-      <c r="B47" s="8"/>
+        <v>109</v>
+      </c>
+      <c r="B47" s="22">
+        <v>25265</v>
+      </c>
       <c r="C47" s="8">
         <f>C41*Assumptions!$B$4</f>
-        <v>30637.644</v>
-      </c>
-      <c r="D47" s="26">
+        <v>30678.408000000003</v>
+      </c>
+      <c r="D47" s="28">
         <f t="shared" si="1"/>
-        <v>30637.644</v>
-      </c>
-      <c r="E47" s="8" t="str">
+        <v>30678.408000000003</v>
+      </c>
+      <c r="E47" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5413.4080000000031</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>110</v>
-      </c>
-      <c r="B48" s="8"/>
+        <v>111</v>
+      </c>
+      <c r="B48" s="22">
+        <v>31280</v>
+      </c>
       <c r="C48" s="8">
         <f>B7*Assumptions!$B$7</f>
         <v>24000</v>
       </c>
-      <c r="D48" s="26">
+      <c r="D48" s="28">
         <f t="shared" si="1"/>
-        <v>24000</v>
-      </c>
-      <c r="E48" s="8" t="str">
+        <v>31280</v>
+      </c>
+      <c r="E48" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>112</v>
-      </c>
-      <c r="B49" s="8"/>
+        <v>113</v>
+      </c>
+      <c r="B49" s="22">
+        <v>20882</v>
+      </c>
       <c r="C49" s="8">
         <f>B7*Assumptions!$B$10</f>
         <v>36000</v>
       </c>
-      <c r="D49" s="26">
+      <c r="D49" s="28">
         <f t="shared" si="1"/>
         <v>36000</v>
       </c>
-      <c r="E49" s="8" t="str">
+      <c r="E49" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>15118</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>114</v>
-      </c>
-      <c r="B50" s="8"/>
+        <v>115</v>
+      </c>
+      <c r="B50" s="22">
+        <v>3180</v>
+      </c>
       <c r="C50" s="8">
         <f>B7*Assumptions!$B$12</f>
         <v>8000</v>
       </c>
-      <c r="D50" s="26">
+      <c r="D50" s="28">
         <f t="shared" si="1"/>
         <v>8000</v>
       </c>
-      <c r="E50" s="8" t="str">
+      <c r="E50" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4820</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>116</v>
-      </c>
-      <c r="B51" s="8"/>
+        <v>117</v>
+      </c>
+      <c r="B51" s="22">
+        <v>21200</v>
+      </c>
       <c r="C51" s="8">
         <f>B7*Assumptions!$B$13</f>
         <v>5000</v>
       </c>
-      <c r="D51" s="26">
+      <c r="D51" s="28">
         <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-      <c r="E51" s="8" t="str">
+        <v>21200</v>
+      </c>
+      <c r="E51" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>118</v>
-      </c>
-      <c r="B52" s="8"/>
+        <v>119</v>
+      </c>
+      <c r="B52" s="22"/>
       <c r="C52" s="8">
         <f>B7*Assumptions!$B$14</f>
         <v>6000</v>
       </c>
-      <c r="D52" s="26">
+      <c r="D52" s="28">
         <f t="shared" si="1"/>
         <v>6000</v>
       </c>
@@ -1931,79 +1970,79 @@
         <v/>
       </c>
       <c r="F52" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="B53" s="24">
-        <f>B41-B22*B25</f>
-        <v>217528.50810372783</v>
-      </c>
-      <c r="C53" s="24">
+      <c r="A53" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" s="26">
+        <f>SUM(B45:B52)</f>
+        <v>217743</v>
+      </c>
+      <c r="C53" s="26">
         <f>SUM(C45:C52)</f>
-        <v>218286.144</v>
-      </c>
-      <c r="D53" s="24">
+        <v>218326.908</v>
+      </c>
+      <c r="D53" s="26">
         <f>SUM(D45:D52)</f>
-        <v>218286.144</v>
-      </c>
-      <c r="E53" s="24">
+        <v>241806.908</v>
+      </c>
+      <c r="E53" s="26">
         <f t="shared" si="0"/>
-        <v>757.63589627217152</v>
+        <v>24063.907999999996</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B54" s="8">
         <f>IFERROR(B53/B7,"")</f>
-        <v>10876.425405186392</v>
+        <v>10887.15</v>
       </c>
       <c r="C54" s="8">
         <f>IFERROR(C53/B7,"")</f>
-        <v>10914.307199999999</v>
+        <v>10916.3454</v>
       </c>
       <c r="D54" s="8">
         <f>IFERROR(D53/B7,"")</f>
-        <v>10914.307199999999</v>
+        <v>12090.3454</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B55" s="18">
         <f>IFERROR(B53/B41,"")</f>
-        <v>0.35501237113402073</v>
+        <v>0.35493375574008679</v>
       </c>
       <c r="C55" s="18">
         <f>IFERROR(C53/C41,"")</f>
-        <v>0.35623846272252524</v>
+        <v>0.3558315477126453</v>
       </c>
       <c r="D55" s="18">
         <f>IF(C37&gt;0,IFERROR(D53/C41,""),"")</f>
-        <v>0.35623846272252524</v>
+        <v>0.39409950477221634</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B56" s="12" t="str">
+      <c r="A56" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B56" s="29" t="str">
         <f>IF(ISNUMBER(B53),IF(D53&gt;B53*(1+Assumptions!$B$24),"OM EXPENSES LIGHT","OM expenses reasonable"),"OM expenses not published")</f>
-        <v>OM expenses reasonable</v>
+        <v>OM EXPENSES LIGHT</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -2012,77 +2051,80 @@
       <c r="F58" s="14"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="25"/>
-      <c r="B59" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C59" s="25" t="s">
+      <c r="A59" s="27"/>
+      <c r="B59" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="D59" s="25"/>
-      <c r="E59" s="25"/>
-      <c r="F59" s="25" t="s">
+      <c r="C59" s="27" t="s">
         <v>92</v>
       </c>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="B60" s="24">
+      <c r="A60" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B60" s="26">
         <f>B41-B53</f>
-        <v>395206.5</v>
-      </c>
-      <c r="C60" s="24">
+        <v>395732.04000000004</v>
+      </c>
+      <c r="C60" s="26">
         <f>IF(C37&gt;0,C41-D53,"")</f>
-        <v>394466.73600000003</v>
+        <v>371761.25200000004</v>
+      </c>
+      <c r="F60" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="22" t="s">
-        <v>126</v>
+      <c r="A61" s="24" t="s">
+        <v>128</v>
       </c>
       <c r="B61" s="18">
         <f>IFERROR(B60/B22,"")</f>
-        <v>5.0700000000000002E-2</v>
+        <v>5.0767420141116106E-2</v>
       </c>
       <c r="C61" s="18">
         <f>IF(C60="","",IFERROR(C60/B22,""))</f>
-        <v>5.0605097626683776E-2</v>
+        <v>4.7692270942912125E-2</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B62" s="19">
         <f>IFERROR(B22/B37,"")</f>
-        <v>12.339999999999998</v>
+        <v>12.879358659158802</v>
       </c>
       <c r="C62" s="19">
         <f>IF(C37&gt;0,IFERROR(B22/C37,""),"")</f>
-        <v>12.339640084596583</v>
+        <v>12.87731609970132</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B63" s="8">
         <f>IFERROR(B60/B7,"")</f>
-        <v>19760.325000000001</v>
+        <v>19786.602000000003</v>
       </c>
       <c r="C63" s="8">
         <f>IF(C60="","",IFERROR(C60/B7,""))</f>
-        <v>19723.336800000001</v>
+        <v>18588.062600000001</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
@@ -2092,7 +2134,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B66" s="8">
         <f>IFERROR(B22*Assumptions!$B$20,"")</f>
@@ -2101,75 +2143,75 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B67" s="8">
         <f>IF(C60="","",IFERROR(PV(Assumptions!$B$22/12,Assumptions!$B$23*12,-C60/Assumptions!$B$21/12),""))</f>
-        <v>4271081.3311352003</v>
+        <v>4025238.1206020089</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="22" t="s">
-        <v>133</v>
+      <c r="A68" s="24" t="s">
+        <v>135</v>
       </c>
       <c r="B68" s="8">
         <f>IFERROR(MIN(B66,B67),"")</f>
-        <v>4271081.3311352003</v>
+        <v>4025238.1206020089</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B69" s="8">
         <f>IFERROR(B22-B68,"")</f>
-        <v>3523918.6688647997</v>
+        <v>3769761.8793979911</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B70" s="8">
         <f>IFERROR(-PMT(Assumptions!$B$22/12,Assumptions!$B$23*12,B68)*12,"")</f>
-        <v>315573.38879999897</v>
+        <v>297409.00159999909</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B71" s="19">
         <f>IFERROR(C60/B70,"")</f>
-        <v>1.2500000000000042</v>
+        <v>1.250000000000004</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B72" s="8">
         <f>IFERROR(C60-B70,"")</f>
-        <v>78893.347200001066</v>
+        <v>74352.25040000095</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B73" s="18">
         <f>IFERROR(B72/B69,"")</f>
-        <v>2.2387959148164983E-2</v>
+        <v>1.9723328098345184E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{12F6186E-C4D8-4BA0-B547-E9354CD5B8FD}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{B6CBA7C1-7645-41FE-BF40-55E46BB2E515}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" r:id="rId2"/>

--- a/files/22-222-228-idaho-ave.xlsx
+++ b/files/22-222-228-idaho-ave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iniculete\LAAA-Deploys\onmarket\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6A8DA51-18C4-4ECD-9EE0-3E3CFBDC10A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA882294-D129-4DAA-9741-E0EA6DDAB3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D5539255-B69F-4543-B41B-0450F8F154A0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{44BFD15A-DA1F-4FBB-9DC4-896D619DD73B}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
@@ -195,7 +195,7 @@
     <t>Data pulled 9/17/2026 from LoopNet public listing + rent roll and expenses read from the listing broker's OM (Lee &amp; Associates, Berzack, rent roll 9/1/2026)</t>
   </si>
   <si>
-    <t>NOTE: Two parcels 222 &amp; 228 Idaho | OM: Unit-by-unit rents sum to exactly $50,436/mo; OM annual $605,232 = 12 x $50,436 (matches).; Unit 228-3 (1+1) is VACANT; its $2,800 is the OM's asking rent, included in current GSR per OM.; Three units are owner occupied and 'can be delivered vacant' (228-1 $2,750, 228-6 $3,595, 228-10 $2,800); the O | OM: Unit-by-unit rents sum to exactly $50,436/mo; OM annual $605,232 = 12 x $50,436 (matches).; Unit 228-3 (1+1) is VACANT; its $2,800 is the OM's asking rent, included in current GSR per OM.; Three units are owner occupied and 'can be delivered vacant' (228-1 $2,750, 228-6 $3,595, 228-10 $2,800); the O</t>
+    <t>NOTE: Two parcels 222 &amp; 228 Idaho | OM: Unit-by-unit rents sum to exactly $50,436/mo; OM annual $605,232 = 12 x $50,436 (matches).; Unit 228-3 (1+1) is VACANT; its $2,800 is the OM's asking rent, included in current GSR per OM.; Three units are owner occupied and 'can be delivered vacant' (228-1 $2,750, 228-6 $3,595, 228-10 $2,800); the O</t>
   </si>
   <si>
     <t>PROPERTY</t>
@@ -679,7 +679,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{795909FD-955F-408B-9F94-8CAF09766150}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0523D41-4439-4D31-BC69-33A33FA5F6FE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -990,7 +990,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4917C3AA-E721-4D18-85F3-44C369FA02A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15445C6-3B1A-4C19-8066-45346573D5F1}">
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1359,7 +1359,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7B119C1-5B8F-45E6-94E8-9F3DDDCBF039}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523EEF8C-7079-4A6D-ADBA-E5E807AD664E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2211,7 +2211,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{B6CBA7C1-7645-41FE-BF40-55E46BB2E515}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{59F4D22D-9FFB-46E3-AEC9-EABE76A58E67}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" r:id="rId2"/>
